--- a/data/availability/projects/madinet-masr/the-butterfly.xlsx
+++ b/data/availability/projects/madinet-masr/the-butterfly.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1059,7 +1059,6 @@
       <c r="G2" t="n">
         <v>38</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1092,7 +1091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1116,7 +1115,6 @@
       <c r="G3" t="n">
         <v>50</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1149,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1173,7 +1171,6 @@
       <c r="G4" t="n">
         <v>90</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1206,7 +1203,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1230,7 +1227,6 @@
       <c r="G5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1287,7 +1283,6 @@
       <c r="G6" t="n">
         <v>212</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1344,7 +1339,6 @@
       <c r="G7" t="n">
         <v>248</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1401,7 +1395,6 @@
       <c r="G8" t="n">
         <v>175</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1458,7 +1451,6 @@
       <c r="G9" t="n">
         <v>240</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/madinet-masr/the-butterfly.xlsx
+++ b/data/availability/projects/madinet-masr/the-butterfly.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
